--- a/partner_results/chebi/ClassMissingCurationStatus_chebi.xlsx
+++ b/partner_results/chebi/ClassMissingCurationStatus_chebi.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rubber particle [chebi]</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>polymer [chebi]</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A polymer consisting of cis-linked prenyl units.</t>
+          <t>A mixture is a chemical substance composed of multiple molecules, at least two of which are of a different kind.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>thiazoles [chebi]</t>
+          <t>organic divalent group [chebi]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>organosulfur heterocyclic compound</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>organic group [chebi]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lars Vogt</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>An azole in which the five-membered heterocyclic aromatic skeleton contains a N atom and one S atom.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,37 +488,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
+          <t>thiazoles [chebi]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>organic group [chebi]</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lars Vogt</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>azole</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>An azole in which the five-membered heterocyclic aromatic skeleton contains a N atom and one S atom.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>polymer [chebi]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A mixture is a chemical substance composed of multiple molecules, at least two of which are of a different kind.</t>
+          <t>A polymer consisting of cis-linked prenyl units.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
